--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,6 +1242,130 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122619838</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56593</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tömme, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>365412</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6624529</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,7 +1247,7 @@
         <v>122619838</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1365,6 +1365,380 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122683812</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S Tömme, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>365378</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6624458</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122683795</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57384</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>S Tömme, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>365643</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6624549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122683784</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57400</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>S Tömme, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>365585</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6624551</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683812</v>
+        <v>122683795</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,37 +1384,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365378</v>
+        <v>365643</v>
       </c>
       <c r="R7" t="n">
-        <v>6624458</v>
+        <v>6624549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,9 +1457,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683795</v>
+        <v>122683812</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,37 +1512,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1542,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365643</v>
+        <v>365378</v>
       </c>
       <c r="R8" t="n">
-        <v>6624549</v>
+        <v>6624458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1575,19 +1585,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683812</v>
+        <v>122683784</v>
       </c>
       <c r="B8" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365378</v>
+        <v>365585</v>
       </c>
       <c r="R8" t="n">
-        <v>6624458</v>
+        <v>6624551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,9 +1585,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1624,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122683784</v>
+        <v>122683812</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,21 +1640,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1660,7 +1670,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1670,10 +1680,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>365585</v>
+        <v>365378</v>
       </c>
       <c r="R9" t="n">
-        <v>6624551</v>
+        <v>6624458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,19 +1713,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683795</v>
+        <v>122683812</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,37 +1384,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365643</v>
+        <v>365378</v>
       </c>
       <c r="R7" t="n">
-        <v>6624549</v>
+        <v>6624458</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,19 +1457,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683812</v>
+        <v>122683784</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,21 +1502,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1542,7 +1532,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1552,10 +1542,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365378</v>
+        <v>365585</v>
       </c>
       <c r="R8" t="n">
-        <v>6624458</v>
+        <v>6624551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,9 +1575,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122683784</v>
+        <v>122683795</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1649,18 +1649,18 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>365585</v>
+        <v>365643</v>
       </c>
       <c r="R9" t="n">
-        <v>6624551</v>
+        <v>6624549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683812</v>
+        <v>122683784</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365378</v>
+        <v>365585</v>
       </c>
       <c r="R7" t="n">
-        <v>6624458</v>
+        <v>6624551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,9 +1457,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683784</v>
+        <v>122683812</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,21 +1512,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1532,7 +1542,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1542,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365585</v>
+        <v>365378</v>
       </c>
       <c r="R8" t="n">
-        <v>6624551</v>
+        <v>6624458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1575,19 +1585,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683784</v>
+        <v>122683812</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365585</v>
+        <v>365378</v>
       </c>
       <c r="R7" t="n">
-        <v>6624551</v>
+        <v>6624458</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,19 +1457,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683812</v>
+        <v>122683795</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,37 +1502,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1552,10 +1542,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365378</v>
+        <v>365643</v>
       </c>
       <c r="R8" t="n">
-        <v>6624458</v>
+        <v>6624549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,9 +1575,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122683795</v>
+        <v>122683784</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1649,18 +1649,18 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>365643</v>
+        <v>365585</v>
       </c>
       <c r="R9" t="n">
-        <v>6624549</v>
+        <v>6624551</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683812</v>
+        <v>122683784</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365378</v>
+        <v>365585</v>
       </c>
       <c r="R7" t="n">
-        <v>6624458</v>
+        <v>6624551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,9 +1457,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683795</v>
+        <v>122683812</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,37 +1512,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1542,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365643</v>
+        <v>365378</v>
       </c>
       <c r="R8" t="n">
-        <v>6624549</v>
+        <v>6624458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1575,19 +1585,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122683784</v>
+        <v>122683795</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1649,18 +1649,18 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>365585</v>
+        <v>365643</v>
       </c>
       <c r="R9" t="n">
-        <v>6624551</v>
+        <v>6624549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683784</v>
+        <v>122683795</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1403,18 +1403,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365585</v>
+        <v>365643</v>
       </c>
       <c r="R7" t="n">
-        <v>6624551</v>
+        <v>6624549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683812</v>
+        <v>122683784</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365378</v>
+        <v>365585</v>
       </c>
       <c r="R8" t="n">
-        <v>6624458</v>
+        <v>6624551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,9 +1585,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1624,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122683795</v>
+        <v>122683812</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,37 +1640,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1670,10 +1680,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>365643</v>
+        <v>365378</v>
       </c>
       <c r="R9" t="n">
-        <v>6624549</v>
+        <v>6624458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,19 +1713,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683784</v>
+        <v>122683812</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365585</v>
+        <v>365378</v>
       </c>
       <c r="R8" t="n">
-        <v>6624551</v>
+        <v>6624458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,19 +1585,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122683812</v>
+        <v>122683784</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1640,21 +1630,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1670,7 +1660,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1680,10 +1670,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>365378</v>
+        <v>365585</v>
       </c>
       <c r="R9" t="n">
-        <v>6624458</v>
+        <v>6624551</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,9 +1703,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683795</v>
+        <v>122683812</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,37 +1384,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365643</v>
+        <v>365378</v>
       </c>
       <c r="R7" t="n">
-        <v>6624549</v>
+        <v>6624458</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,19 +1457,9 @@
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683812</v>
+        <v>122683795</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,37 +1502,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1552,10 +1542,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365378</v>
+        <v>365643</v>
       </c>
       <c r="R8" t="n">
-        <v>6624458</v>
+        <v>6624549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,9 +1575,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5956-2025 artfynd.xlsx
+++ b/artfynd/A 5956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -954,14 +954,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16959138</v>
+        <v>16959137</v>
       </c>
       <c r="B4" t="n">
         <v>96334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myrbråten, 700 m VNV om, Vrm</t>
+          <t>Myrbråten, 550 m VNV om, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365234.2390877325</v>
+        <v>365401.0864800403</v>
       </c>
       <c r="R4" t="n">
-        <v>6624468.002082705</v>
+        <v>6624469.037099285</v>
       </c>
       <c r="S4" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>S-Arv-0647</t>
+          <t>S-Arv-0646</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>260 bladrosetter med 33 blomstänglar, sju spridda grupper från 443-973 i nordöst till 367-931 i sydväst (RT 90)</t>
+          <t>10 bladrosetter med 2 blomstänglar, även några bladrosetter vid 456-186 (RT 90)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig granskog med inslag av äldre tallar</t>
+          <t>äldre mager barrskog med gran och tall på bergbunden mark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1099,64 +1099,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16959137</v>
+        <v>122619838</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Myrbråten, 550 m VNV om, Vrm</t>
+          <t>Tömme, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>365401.0864800403</v>
+        <v>365412</v>
       </c>
       <c r="R5" t="n">
-        <v>6624469.037099285</v>
+        <v>6624529</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1181,34 +1179,24 @@
           <t>Gunnarskog</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>S-Arv-0646</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-12-23</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-12-23</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 bladrosetter med 2 blomstänglar, även några bladrosetter vid 456-186 (RT 90)</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1219,35 +1207,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre mager barrskog med gran och tall på bergbunden mark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122619838</v>
+        <v>122683812</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,53 +1235,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tömme, Vrm</t>
+          <t>S Tömme, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>365412</v>
+        <v>365378</v>
       </c>
       <c r="R6" t="n">
-        <v>6624529</v>
+        <v>6624458</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1326,22 +1309,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1368,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122683812</v>
+        <v>122683795</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,37 +1357,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1424,10 +1397,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>365378</v>
+        <v>365643</v>
       </c>
       <c r="R7" t="n">
-        <v>6624458</v>
+        <v>6624549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1457,9 +1430,19 @@
           <t>2025-02-18</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122683795</v>
+        <v>122683784</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,16 +1485,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1521,18 +1504,18 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1542,10 +1525,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>365643</v>
+        <v>365585</v>
       </c>
       <c r="R8" t="n">
-        <v>6624549</v>
+        <v>6624551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1611,134 +1594,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122683784</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>S Tömme, Vrm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>365585</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6624551</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Gunnarskog</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Torbjörn Westerberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Torbjörn Westerberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
